--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -36850,6 +36850,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1587">
+      <c r="A1587" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1587" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C1587" t="n">
+        <v>4.73000001907349</v>
+      </c>
+      <c r="D1587" t="n">
+        <v>4.61499977111816</v>
+      </c>
+      <c r="E1587" t="n">
+        <v>4.73000001907349</v>
+      </c>
+      <c r="F1587" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="G1587" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -36873,6 +36873,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1588">
+      <c r="A1588" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1588" t="n">
+        <v>81257</v>
+      </c>
+      <c r="C1588" t="n">
+        <v>4.67000007629395</v>
+      </c>
+      <c r="D1588" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E1588" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F1588" t="n">
+        <v>4.60500001907349</v>
+      </c>
+      <c r="G1588" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -36896,6 +36896,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1589">
+      <c r="A1589" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1589" t="n">
+        <v>100869</v>
+      </c>
+      <c r="C1589" t="n">
+        <v>4.75500011444092</v>
+      </c>
+      <c r="D1589" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E1589" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F1589" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="G1589" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -36919,6 +36919,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1590">
+      <c r="A1590" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1590" t="n">
+        <v>46536</v>
+      </c>
+      <c r="C1590" t="n">
+        <v>4.76000022888184</v>
+      </c>
+      <c r="D1590" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="E1590" t="n">
+        <v>4.67500019073486</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>4.6399998664856</v>
+      </c>
+      <c r="G1590" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -36760,22 +36760,22 @@
     </row>
     <row r="1583">
       <c r="A1583" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1583" t="n">
-        <v>65876</v>
+        <v>28747</v>
       </c>
       <c r="C1583" t="n">
-        <v>4.78499984741211</v>
+        <v>4.84000015258789</v>
       </c>
       <c r="D1583" t="n">
-        <v>4.71000003814697</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="E1583" t="n">
-        <v>4.73000001907349</v>
+        <v>4.84000015258789</v>
       </c>
       <c r="F1583" t="n">
-        <v>4.75</v>
+        <v>4.76000022888184</v>
       </c>
       <c r="G1583" t="s">
         <v>7</v>
@@ -36783,22 +36783,22 @@
     </row>
     <row r="1584">
       <c r="A1584" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1584" t="n">
-        <v>60472</v>
+        <v>65876</v>
       </c>
       <c r="C1584" t="n">
-        <v>4.76999998092651</v>
+        <v>4.78499984741211</v>
       </c>
       <c r="D1584" t="n">
-        <v>4.70499992370605</v>
+        <v>4.71000003814697</v>
       </c>
       <c r="E1584" t="n">
+        <v>4.73000001907349</v>
+      </c>
+      <c r="F1584" t="n">
         <v>4.75</v>
-      </c>
-      <c r="F1584" t="n">
-        <v>4.7350001335144</v>
       </c>
       <c r="G1584" t="s">
         <v>7</v>
@@ -36806,22 +36806,22 @@
     </row>
     <row r="1585">
       <c r="A1585" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1585" t="n">
-        <v>53933</v>
+        <v>60472</v>
       </c>
       <c r="C1585" t="n">
-        <v>4.80999994277954</v>
+        <v>4.76999998092651</v>
       </c>
       <c r="D1585" t="n">
-        <v>4.6399998664856</v>
+        <v>4.70499992370605</v>
       </c>
       <c r="E1585" t="n">
-        <v>4.80999994277954</v>
+        <v>4.75</v>
       </c>
       <c r="F1585" t="n">
-        <v>4.6399998664856</v>
+        <v>4.7350001335144</v>
       </c>
       <c r="G1585" t="s">
         <v>7</v>
@@ -36829,22 +36829,22 @@
     </row>
     <row r="1586">
       <c r="A1586" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1586" t="n">
-        <v>45632</v>
+        <v>53933</v>
       </c>
       <c r="C1586" t="n">
-        <v>4.71999979019165</v>
+        <v>4.80999994277954</v>
       </c>
       <c r="D1586" t="n">
-        <v>4.61999988555908</v>
+        <v>4.6399998664856</v>
       </c>
       <c r="E1586" t="n">
-        <v>4.71999979019165</v>
+        <v>4.80999994277954</v>
       </c>
       <c r="F1586" t="n">
-        <v>4.65500020980835</v>
+        <v>4.6399998664856</v>
       </c>
       <c r="G1586" t="s">
         <v>7</v>
@@ -36852,22 +36852,22 @@
     </row>
     <row r="1587">
       <c r="A1587" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1587" t="n">
-        <v>46107</v>
+        <v>45632</v>
       </c>
       <c r="C1587" t="n">
-        <v>4.73000001907349</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="D1587" t="n">
-        <v>4.61499977111816</v>
+        <v>4.61999988555908</v>
       </c>
       <c r="E1587" t="n">
-        <v>4.73000001907349</v>
+        <v>4.71999979019165</v>
       </c>
       <c r="F1587" t="n">
-        <v>4.71500015258789</v>
+        <v>4.65500020980835</v>
       </c>
       <c r="G1587" t="s">
         <v>7</v>
@@ -36875,22 +36875,22 @@
     </row>
     <row r="1588">
       <c r="A1588" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1588" t="n">
-        <v>81257</v>
+        <v>46107</v>
       </c>
       <c r="C1588" t="n">
-        <v>4.67000007629395</v>
+        <v>4.73000001907349</v>
       </c>
       <c r="D1588" t="n">
-        <v>4.55999994277954</v>
+        <v>4.61499977111816</v>
       </c>
       <c r="E1588" t="n">
-        <v>4.61999988555908</v>
+        <v>4.73000001907349</v>
       </c>
       <c r="F1588" t="n">
-        <v>4.60500001907349</v>
+        <v>4.71500015258789</v>
       </c>
       <c r="G1588" t="s">
         <v>7</v>
@@ -36898,22 +36898,22 @@
     </row>
     <row r="1589">
       <c r="A1589" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1589" t="n">
-        <v>100869</v>
+        <v>81257</v>
       </c>
       <c r="C1589" t="n">
-        <v>4.75500011444092</v>
+        <v>4.67000007629395</v>
       </c>
       <c r="D1589" t="n">
         <v>4.55999994277954</v>
       </c>
       <c r="E1589" t="n">
-        <v>4.55999994277954</v>
+        <v>4.61999988555908</v>
       </c>
       <c r="F1589" t="n">
-        <v>4.71500015258789</v>
+        <v>4.60500001907349</v>
       </c>
       <c r="G1589" t="s">
         <v>7</v>
@@ -36921,24 +36921,47 @@
     </row>
     <row r="1590">
       <c r="A1590" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1590" t="n">
-        <v>46536</v>
+        <v>100869</v>
       </c>
       <c r="C1590" t="n">
-        <v>4.76000022888184</v>
+        <v>4.75500011444092</v>
       </c>
       <c r="D1590" t="n">
-        <v>4.625</v>
+        <v>4.55999994277954</v>
       </c>
       <c r="E1590" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F1590" t="n">
+        <v>4.71500015258789</v>
+      </c>
+      <c r="G1590" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1591" t="n">
+        <v>93516</v>
+      </c>
+      <c r="C1591" t="n">
         <v>4.67500019073486</v>
       </c>
-      <c r="F1590" t="n">
-        <v>4.6399998664856</v>
-      </c>
-      <c r="G1590" t="s">
+      <c r="D1591" t="n">
+        <v>4.55000019073486</v>
+      </c>
+      <c r="E1591" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F1591" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G1591" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -41772,7 +41772,7 @@
         <v>46286.2916666667</v>
       </c>
       <c r="B1593" t="n">
-        <v>68280</v>
+        <v>83280</v>
       </c>
       <c r="C1593" t="n">
         <v>4.69999980926514</v>
@@ -41790,6 +41790,32 @@
         <v>4.69999980926514</v>
       </c>
       <c r="H1593" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1594" t="n">
+        <v>62490</v>
+      </c>
+      <c r="C1594" t="n">
+        <v>4.69999980926514</v>
+      </c>
+      <c r="D1594" t="n">
+        <v>4.58500003814697</v>
+      </c>
+      <c r="E1594" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F1594" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="G1594" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="H1594" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -41819,6 +41819,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1595">
+      <c r="A1595" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1595" t="n">
+        <v>30582</v>
+      </c>
+      <c r="C1595" t="n">
+        <v>4.65000009536743</v>
+      </c>
+      <c r="D1595" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E1595" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="F1595" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G1595" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="H1595" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -41845,6 +41845,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1596">
+      <c r="A1596" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1596" t="n">
+        <v>224499</v>
+      </c>
+      <c r="C1596" t="n">
+        <v>4.82000017166138</v>
+      </c>
+      <c r="D1596" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="E1596" t="n">
+        <v>4.65999984741211</v>
+      </c>
+      <c r="F1596" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="G1596" t="n">
+        <v>4.625</v>
+      </c>
+      <c r="H1596" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -41871,6 +41871,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1597">
+      <c r="A1597" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1597" t="n">
+        <v>316889</v>
+      </c>
+      <c r="C1597" t="n">
+        <v>4.89499998092651</v>
+      </c>
+      <c r="D1597" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="E1597" t="n">
+        <v>4.61999988555908</v>
+      </c>
+      <c r="F1597" t="n">
+        <v>4.88000011444092</v>
+      </c>
+      <c r="G1597" t="n">
+        <v>4.88000011444092</v>
+      </c>
+      <c r="H1597" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -41949,6 +41949,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1600">
+      <c r="A1600" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1600" t="n">
+        <v>243313</v>
+      </c>
+      <c r="C1600" t="n">
+        <v>5.34999990463257</v>
+      </c>
+      <c r="D1600" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E1600" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F1600" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="G1600" t="n">
+        <v>5.32000017166138</v>
+      </c>
+      <c r="H1600" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -37234,8 +37234,31 @@
       <c r="E1603" t="n">
         <v>5.30000019073486</v>
       </c>
-      <c r="F1603"/>
+      <c r="F1603" t="n">
+        <v>5.05000019073486</v>
+      </c>
       <c r="G1603" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1604" t="n">
+        <v>112714</v>
+      </c>
+      <c r="C1604" t="n">
+        <v>5.28999996185303</v>
+      </c>
+      <c r="D1604" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1604" t="n">
+        <v>5.28999996185303</v>
+      </c>
+      <c r="F1604"/>
+      <c r="G1604" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -37257,8 +37257,31 @@
       <c r="E1604" t="n">
         <v>5.28999996185303</v>
       </c>
-      <c r="F1604"/>
+      <c r="F1604" t="n">
+        <v>5.23999977111816</v>
+      </c>
       <c r="G1604" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1605" t="n">
+        <v>59022</v>
+      </c>
+      <c r="C1605" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D1605" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="E1605" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="F1605"/>
+      <c r="G1605" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -37280,8 +37280,31 @@
       <c r="E1605" t="n">
         <v>5.25</v>
       </c>
-      <c r="F1605"/>
+      <c r="F1605" t="n">
+        <v>5.15000009536743</v>
+      </c>
       <c r="G1605" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1606" t="n">
+        <v>56956</v>
+      </c>
+      <c r="C1606" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="D1606" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="E1606" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="F1606"/>
+      <c r="G1606" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -37303,8 +37303,31 @@
       <c r="E1606" t="n">
         <v>5.05999994277954</v>
       </c>
-      <c r="F1606"/>
+      <c r="F1606" t="n">
+        <v>5.05999994277954</v>
+      </c>
       <c r="G1606" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1607" t="n">
+        <v>73928</v>
+      </c>
+      <c r="C1607" t="n">
+        <v>5.17000007629395</v>
+      </c>
+      <c r="D1607" t="n">
+        <v>5.09000015258789</v>
+      </c>
+      <c r="E1607" t="n">
+        <v>5.09999990463257</v>
+      </c>
+      <c r="F1607"/>
+      <c r="G1607" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -37333,6 +37333,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1608">
+      <c r="A1608" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1608" t="n">
+        <v>83092</v>
+      </c>
+      <c r="C1608" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D1608" t="n">
+        <v>5.1100001335144</v>
+      </c>
+      <c r="E1608" t="n">
+        <v>5.23000001907349</v>
+      </c>
+      <c r="F1608" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="G1608" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -42220,7 +42220,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="D1610" t="n">
-        <v>5.32999992370605</v>
+        <v>5.30999994277954</v>
       </c>
       <c r="E1610" t="n">
         <v>5.34999990463257</v>
@@ -42232,6 +42232,32 @@
         <v>5.30999994277954</v>
       </c>
       <c r="H1610" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1611" t="n">
+        <v>36532</v>
+      </c>
+      <c r="C1611" t="n">
+        <v>5.34000015258789</v>
+      </c>
+      <c r="D1611" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="E1611" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="F1611" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="G1611" t="n">
+        <v>5.23999977111816</v>
+      </c>
+      <c r="H1611" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -42240,7 +42240,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B1611" t="n">
-        <v>36532</v>
+        <v>38632</v>
       </c>
       <c r="C1611" t="n">
         <v>5.34000015258789</v>
@@ -42258,6 +42258,32 @@
         <v>5.23999977111816</v>
       </c>
       <c r="H1611" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1612" t="n">
+        <v>281698</v>
+      </c>
+      <c r="C1612" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="D1612" t="n">
+        <v>5.03000020980835</v>
+      </c>
+      <c r="E1612" t="n">
+        <v>5.11999988555908</v>
+      </c>
+      <c r="F1612" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="G1612" t="n">
+        <v>5.07000017166138</v>
+      </c>
+      <c r="H1612" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47126,6 +47126,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1613">
+      <c r="A1613" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1613" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1613" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="D1613" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E1613" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="F1613" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="G1613" t="n">
+        <v>4.98000001907349</v>
+      </c>
+      <c r="H1613" t="n">
+        <v>42502</v>
+      </c>
+      <c r="I1613" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1614" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1614" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="D1614" t="n">
+        <v>5.05999994277954</v>
+      </c>
+      <c r="E1614" t="n">
+        <v>4.90000009536743</v>
+      </c>
+      <c r="F1614" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="G1614" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="H1614" t="n">
+        <v>67715</v>
+      </c>
+      <c r="I1614" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47184,6 +47184,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1615">
+      <c r="A1615" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1615" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1615" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="D1615" t="n">
+        <v>5.21000003814697</v>
+      </c>
+      <c r="E1615" t="n">
+        <v>5.01000022888184</v>
+      </c>
+      <c r="F1615" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="G1615" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="H1615" t="n">
+        <v>109352</v>
+      </c>
+      <c r="I1615" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47195,7 +47195,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="D1615" t="n">
-        <v>5.21000003814697</v>
+        <v>5.21999979019165</v>
       </c>
       <c r="E1615" t="n">
         <v>5.01000022888184</v>
@@ -47207,9 +47207,38 @@
         <v>5.21999979019165</v>
       </c>
       <c r="H1615" t="n">
-        <v>109352</v>
+        <v>111203</v>
       </c>
       <c r="I1615" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1616" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1616" t="n">
+        <v>5.21999979019165</v>
+      </c>
+      <c r="D1616" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="E1616" t="n">
+        <v>5.17000007629395</v>
+      </c>
+      <c r="F1616" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="G1616" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="H1616" t="n">
+        <v>28906</v>
+      </c>
+      <c r="I1616" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47242,6 +47242,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1617">
+      <c r="A1617" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1617" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1617" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="D1617" t="n">
+        <v>5.3600001335144</v>
+      </c>
+      <c r="E1617" t="n">
+        <v>5.19999980926514</v>
+      </c>
+      <c r="F1617" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="G1617" t="n">
+        <v>5.26000022888184</v>
+      </c>
+      <c r="H1617" t="n">
+        <v>28189</v>
+      </c>
+      <c r="I1617" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47271,6 +47271,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1618">
+      <c r="A1618" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1618" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1618" t="n">
+        <v>5.34999990463257</v>
+      </c>
+      <c r="D1618" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="E1618" t="n">
+        <v>5.30000019073486</v>
+      </c>
+      <c r="F1618" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="G1618" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="H1618" t="n">
+        <v>388103</v>
+      </c>
+      <c r="I1618" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47300,6 +47300,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1619">
+      <c r="A1619" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1619" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1619" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="D1619" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="E1619" t="n">
+        <v>5.53999996185303</v>
+      </c>
+      <c r="F1619" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="G1619" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="H1619" t="n">
+        <v>111618</v>
+      </c>
+      <c r="I1619" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47329,6 +47329,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1620">
+      <c r="A1620" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1620" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1620" t="n">
+        <v>5.69000005722046</v>
+      </c>
+      <c r="D1620" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="E1620" t="n">
+        <v>5.6399998664856</v>
+      </c>
+      <c r="F1620" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="G1620" t="n">
+        <v>5.69999980926514</v>
+      </c>
+      <c r="H1620" t="n">
+        <v>92693</v>
+      </c>
+      <c r="I1620" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47340,7 +47340,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="D1620" t="n">
-        <v>5.76000022888184</v>
+        <v>5.76999998092651</v>
       </c>
       <c r="E1620" t="n">
         <v>5.6399998664856</v>
@@ -47355,6 +47355,35 @@
         <v>92693</v>
       </c>
       <c r="I1620" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1621" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1621" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="D1621" t="n">
+        <v>5.76000022888184</v>
+      </c>
+      <c r="E1621" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="F1621" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="G1621" t="n">
+        <v>5.71999979019165</v>
+      </c>
+      <c r="H1621" t="n">
+        <v>52257</v>
+      </c>
+      <c r="I1621" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GVS.MI.xlsx
+++ b/data/GVS.MI.xlsx
@@ -47387,6 +47387,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1622">
+      <c r="A1622" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1622" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1622" t="n">
+        <v>5.65999984741211</v>
+      </c>
+      <c r="D1622" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="E1622" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="F1622" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="G1622" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="H1622" t="n">
+        <v>57604</v>
+      </c>
+      <c r="I1622" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
